--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_maule.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_maule.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>14.49571230905238</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>14.48831164995497</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>16.54750476190476</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>15.12929194364823</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>11.79596814145802</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>16.24832000000001</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>13.64137374610093</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>16.3745864097925</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>13.51159111033693</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>13.70593566183467</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>16.66666666666667</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>14.18325549996227</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>11.09442035289399</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>12.10486296791444</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -713,9 +666,6 @@
       <c r="E16">
         <v>13.25474968797671</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -735,9 +685,6 @@
       <c r="E17">
         <v>17.04167390762981</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -757,9 +704,6 @@
       <c r="E18">
         <v>14.99397732932528</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -779,9 +723,6 @@
       <c r="E19">
         <v>11.78173451692106</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,9 +742,6 @@
       <c r="E20">
         <v>13.07762960346197</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,9 +761,6 @@
       <c r="E21">
         <v>13.6792800537846</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -845,9 +780,6 @@
       <c r="E22">
         <v>13.89374999999999</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -867,9 +799,6 @@
       <c r="E23">
         <v>12.89879840259269</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -889,9 +818,6 @@
       <c r="E24">
         <v>15.84508373515696</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -911,9 +837,6 @@
       <c r="E25">
         <v>10.61359573827938</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -933,9 +856,6 @@
       <c r="E26">
         <v>11.93094308535405</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -955,9 +875,6 @@
       <c r="E27">
         <v>11.06365229595445</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -977,9 +894,6 @@
       <c r="E28">
         <v>16.3223023750777</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -999,9 +913,6 @@
       <c r="E29">
         <v>16.85093067419099</v>
       </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1021,9 +932,6 @@
       <c r="E30">
         <v>14.99999999999999</v>
       </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1042,9 +950,6 @@
       </c>
       <c r="E31">
         <v>13.88190743282454</v>
-      </c>
-      <c r="F31" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_maule.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_maule.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -556,399 +556,418 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B11">
-        <v>701996</v>
+        <v>702888</v>
       </c>
       <c r="C11">
-        <v>617378.5</v>
+        <v>619050</v>
       </c>
       <c r="D11">
-        <v>84617.5</v>
+        <v>83838</v>
       </c>
       <c r="E11">
-        <v>13.70593566183467</v>
+        <v>13.54300944996365</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="B12">
-        <v>700000</v>
+        <v>701996</v>
       </c>
       <c r="C12">
-        <v>600000</v>
+        <v>617378.5</v>
       </c>
       <c r="D12">
-        <v>100000</v>
+        <v>84617.5</v>
       </c>
       <c r="E12">
-        <v>16.66666666666667</v>
+        <v>13.70593566183467</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="B13">
-        <v>688400</v>
+        <v>700000</v>
       </c>
       <c r="C13">
-        <v>602890.5</v>
+        <v>600000</v>
       </c>
       <c r="D13">
-        <v>85509.5</v>
+        <v>100000</v>
       </c>
       <c r="E13">
-        <v>14.18325549996227</v>
+        <v>16.66666666666667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Curepto</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="B14">
-        <v>673000</v>
+        <v>688400</v>
       </c>
       <c r="C14">
-        <v>605791</v>
+        <v>602890.5</v>
       </c>
       <c r="D14">
-        <v>67209</v>
+        <v>85509.5</v>
       </c>
       <c r="E14">
-        <v>11.09442035289399</v>
+        <v>14.18325549996227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="B15">
-        <v>670835.5</v>
+        <v>673000</v>
       </c>
       <c r="C15">
-        <v>598400</v>
+        <v>605791</v>
       </c>
       <c r="D15">
-        <v>72435.5</v>
+        <v>67209</v>
       </c>
       <c r="E15">
-        <v>12.10486296791444</v>
+        <v>11.09442035289399</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Molina</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="B16">
-        <v>653344</v>
+        <v>670835.5</v>
       </c>
       <c r="C16">
-        <v>576880</v>
+        <v>598400</v>
       </c>
       <c r="D16">
-        <v>76464</v>
+        <v>72435.5</v>
       </c>
       <c r="E16">
-        <v>13.25474968797671</v>
+        <v>12.10486296791444</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="B17">
-        <v>653288</v>
+        <v>653344</v>
       </c>
       <c r="C17">
-        <v>558167</v>
+        <v>576880</v>
       </c>
       <c r="D17">
-        <v>95121</v>
+        <v>76464</v>
       </c>
       <c r="E17">
-        <v>17.04167390762981</v>
+        <v>13.25474968797671</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="B18">
-        <v>651089</v>
+        <v>653288</v>
       </c>
       <c r="C18">
-        <v>566194</v>
+        <v>558167</v>
       </c>
       <c r="D18">
-        <v>84895</v>
+        <v>95121</v>
       </c>
       <c r="E18">
-        <v>14.99397732932528</v>
+        <v>17.04167390762981</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="B19">
-        <v>651028</v>
+        <v>651089</v>
       </c>
       <c r="C19">
-        <v>582410</v>
+        <v>566194</v>
       </c>
       <c r="D19">
-        <v>68618</v>
+        <v>84895</v>
       </c>
       <c r="E19">
-        <v>11.78173451692106</v>
+        <v>14.99397732932528</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="B20">
-        <v>640189</v>
+        <v>651028</v>
       </c>
       <c r="C20">
-        <v>566150</v>
+        <v>582410</v>
       </c>
       <c r="D20">
-        <v>74039</v>
+        <v>68618</v>
       </c>
       <c r="E20">
-        <v>13.07762960346197</v>
+        <v>11.78173451692106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hualañé</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="B21">
-        <v>639999</v>
+        <v>640189</v>
       </c>
       <c r="C21">
-        <v>562986.5</v>
+        <v>566150</v>
       </c>
       <c r="D21">
-        <v>77012.5</v>
+        <v>74039</v>
       </c>
       <c r="E21">
-        <v>13.6792800537846</v>
+        <v>13.07762960346197</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>Hualañé</t>
         </is>
       </c>
       <c r="B22">
-        <v>637805</v>
+        <v>639999</v>
       </c>
       <c r="C22">
-        <v>560000</v>
+        <v>562986.5</v>
       </c>
       <c r="D22">
-        <v>77805</v>
+        <v>77012.5</v>
       </c>
       <c r="E22">
-        <v>13.89374999999999</v>
+        <v>13.6792800537846</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="B23">
-        <v>637500</v>
+        <v>637805</v>
       </c>
       <c r="C23">
-        <v>564665</v>
+        <v>560000</v>
       </c>
       <c r="D23">
-        <v>72835</v>
+        <v>77805</v>
       </c>
       <c r="E23">
-        <v>12.89879840259269</v>
+        <v>13.89374999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="B24">
-        <v>628130</v>
+        <v>637500</v>
       </c>
       <c r="C24">
-        <v>542215.5</v>
+        <v>564665</v>
       </c>
       <c r="D24">
-        <v>85914.5</v>
+        <v>72835</v>
       </c>
       <c r="E24">
-        <v>15.84508373515696</v>
+        <v>12.89879840259269</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chanco</t>
+          <t>Retiro</t>
         </is>
       </c>
       <c r="B25">
-        <v>625000</v>
+        <v>628130</v>
       </c>
       <c r="C25">
-        <v>565030</v>
+        <v>542215.5</v>
       </c>
       <c r="D25">
-        <v>59970</v>
+        <v>85914.5</v>
       </c>
       <c r="E25">
-        <v>10.61359573827938</v>
+        <v>15.84508373515696</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Teno</t>
+          <t>Chanco</t>
         </is>
       </c>
       <c r="B26">
         <v>625000</v>
       </c>
       <c r="C26">
-        <v>558380</v>
+        <v>565030</v>
       </c>
       <c r="D26">
-        <v>66620</v>
+        <v>59970</v>
       </c>
       <c r="E26">
-        <v>11.93094308535405</v>
+        <v>10.61359573827938</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>Teno</t>
         </is>
       </c>
       <c r="B27">
-        <v>620416</v>
+        <v>625000</v>
       </c>
       <c r="C27">
-        <v>558613</v>
+        <v>558380</v>
       </c>
       <c r="D27">
-        <v>61803</v>
+        <v>66620</v>
       </c>
       <c r="E27">
-        <v>11.06365229595445</v>
+        <v>11.93094308535405</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Longaví</t>
         </is>
       </c>
       <c r="B28">
-        <v>617590</v>
+        <v>620416</v>
       </c>
       <c r="C28">
-        <v>530930</v>
+        <v>558613</v>
       </c>
       <c r="D28">
-        <v>86660</v>
+        <v>61803</v>
       </c>
       <c r="E28">
-        <v>16.3223023750777</v>
+        <v>11.06365229595445</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Río Claro</t>
+          <t>Vichuquén</t>
         </is>
       </c>
       <c r="B29">
-        <v>607938</v>
+        <v>617590</v>
       </c>
       <c r="C29">
-        <v>520268</v>
+        <v>530930</v>
       </c>
       <c r="D29">
-        <v>87670</v>
+        <v>86660</v>
       </c>
       <c r="E29">
-        <v>16.85093067419099</v>
+        <v>16.3223023750777</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Empedrado</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="B30">
-        <v>575000</v>
+        <v>607938</v>
       </c>
       <c r="C30">
-        <v>500000</v>
+        <v>520268</v>
       </c>
       <c r="D30">
-        <v>75000</v>
+        <v>87670</v>
       </c>
       <c r="E30">
-        <v>14.99999999999999</v>
+        <v>16.85093067419099</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rauco</t>
+          <t>Empedrado</t>
         </is>
       </c>
       <c r="B31">
         <v>575000</v>
       </c>
       <c r="C31">
+        <v>500000</v>
+      </c>
+      <c r="D31">
+        <v>75000</v>
+      </c>
+      <c r="E31">
+        <v>14.99999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>575000</v>
+      </c>
+      <c r="C32">
         <v>504909</v>
       </c>
-      <c r="D31">
+      <c r="D32">
         <v>70091</v>
       </c>
-      <c r="E31">
+      <c r="E32">
         <v>13.88190743282454</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_maule.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_maule.xlsx
@@ -978,7 +978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -987,310 +987,215 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>651089</v>
+          <t>Curepto</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chanco</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>625000</v>
+          <t>Empedrado</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colbún</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>713993</v>
+          <t>Pencahue</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Constitución</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>755110</v>
+          <t>Linares</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Curepto</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>673000</v>
+          <t>Longaví</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Curicó</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>703773</v>
+          <t>Talca</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Empedrado</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>575000</v>
+          <t>Chanco</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hualañé</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>639999</v>
+          <t>Pelluhue</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Licantén</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>733409.5</v>
+          <t>Constitución</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Linares</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>701996</v>
+          <t>Licantén</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Longaví</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>620416</v>
+          <t>Vichuquén</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>775280.5</v>
+          <t>Cauquenes</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Molina</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>653344</v>
+          <t>Río Claro</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Parral</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>653288</v>
+          <t>Pelarco</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pelarco</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>700000</v>
+          <t>San Javier</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pelluhue</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>764843</v>
+          <t>Villa Alegre</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pencahue</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>715527</v>
+          <t>Yerbas Buenas</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rauco</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>575000</v>
+          <t>Maule</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Retiro</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>628130</v>
+          <t>San Rafael</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Río Claro</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>607938</v>
+          <t>Sagrada Familia</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Romeral</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>637805</v>
+          <t>Retiro</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>640189</v>
+          <t>Curicó</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>San Clemente</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>688400</v>
+          <t>Molina</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>San Javier</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>670835.5</v>
+          <t>Colbún</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>San Rafael</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>726552</v>
+          <t>San Clemente</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Talca</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>825000</v>
+          <t>Hualañé</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Teno</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>625000</v>
+          <t>Rauco</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>617590</v>
+          <t>Teno</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>651028</v>
+          <t>Romeral</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>637500</v>
+          <t>Parral</t>
+        </is>
       </c>
     </row>
   </sheetData>
